--- a/experiments/04_lora_finetuning/report/epoch_ablation.xlsx
+++ b/experiments/04_lora_finetuning/report/epoch_ablation.xlsx
@@ -551,22 +551,22 @@
   <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -857,22 +857,22 @@
   <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/experiments/04_lora_finetuning/report/epoch_ablation.xlsx
+++ b/experiments/04_lora_finetuning/report/epoch_ablation.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,8 +27,14 @@
       <scheme val="minor"/>
     </font>
     <font/>
+    <font>
+      <color rgb="009C0006"/>
+    </font>
+    <font>
+      <color rgb="00006100"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -37,26 +43,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor rgb="FF00B050"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -163,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -174,13 +174,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -702,34 +699,34 @@
       <c r="F3" s="6" t="n">
         <v>0.7812</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="G3" s="5" t="n">
         <v>41.32</v>
       </c>
-      <c r="H3" s="8" t="n">
+      <c r="H3" s="7" t="n">
         <v>69.37</v>
       </c>
-      <c r="I3" s="8" t="n">
+      <c r="I3" s="7" t="n">
         <v>54.29</v>
       </c>
-      <c r="J3" s="8" t="n">
+      <c r="J3" s="7" t="n">
         <v>0.8905</v>
       </c>
-      <c r="K3" s="8" t="n">
+      <c r="K3" s="7" t="n">
         <v>0.7884</v>
       </c>
-      <c r="L3" s="8" t="n">
+      <c r="L3" s="7" t="n">
         <v>41.88</v>
       </c>
-      <c r="M3" s="7" t="n">
+      <c r="M3" s="5" t="n">
         <v>69.23</v>
       </c>
-      <c r="N3" s="8" t="n">
+      <c r="N3" s="7" t="n">
         <v>54.29</v>
       </c>
-      <c r="O3" s="7" t="n">
+      <c r="O3" s="5" t="n">
         <v>0.89</v>
       </c>
-      <c r="P3" s="7" t="n">
+      <c r="P3" s="5" t="n">
         <v>0.7866</v>
       </c>
     </row>
@@ -748,40 +745,40 @@
       <c r="D4" s="6" t="n">
         <v>82.66</v>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E4" s="5" t="n">
         <v>0.9074</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>0.8012</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="G4" s="5" t="n">
         <v>58.27</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H4" s="5" t="n">
         <v>79.09</v>
       </c>
-      <c r="I4" s="8" t="n">
+      <c r="I4" s="7" t="n">
         <v>84.68000000000001</v>
       </c>
-      <c r="J4" s="8" t="n">
+      <c r="J4" s="7" t="n">
         <v>0.91</v>
       </c>
-      <c r="K4" s="8" t="n">
+      <c r="K4" s="7" t="n">
         <v>0.8129</v>
       </c>
-      <c r="L4" s="8" t="n">
+      <c r="L4" s="7" t="n">
         <v>58.64</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="7" t="n">
         <v>79.45999999999999</v>
       </c>
-      <c r="N4" s="7" t="n">
+      <c r="N4" s="5" t="n">
         <v>84.39</v>
       </c>
       <c r="O4" s="6" t="n">
         <v>0.9071</v>
       </c>
-      <c r="P4" s="7" t="n">
+      <c r="P4" s="5" t="n">
         <v>0.8109</v>
       </c>
     </row>
@@ -800,40 +797,40 @@
       <c r="D5" s="6" t="n">
         <v>59.73</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="5" t="n">
         <v>0.8904</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>0.7043</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="G5" s="5" t="n">
         <v>41.82</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H5" s="5" t="n">
         <v>69.33</v>
       </c>
-      <c r="I5" s="8" t="n">
+      <c r="I5" s="7" t="n">
         <v>65.14</v>
       </c>
-      <c r="J5" s="8" t="n">
+      <c r="J5" s="7" t="n">
         <v>0.892</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>0.7043</v>
       </c>
-      <c r="L5" s="8" t="n">
+      <c r="L5" s="7" t="n">
         <v>42.01</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="7" t="n">
         <v>69.64</v>
       </c>
-      <c r="N5" s="7" t="n">
+      <c r="N5" s="5" t="n">
         <v>63.51</v>
       </c>
       <c r="O5" s="6" t="n">
         <v>0.8855</v>
       </c>
-      <c r="P5" s="8" t="n">
+      <c r="P5" s="7" t="n">
         <v>0.7082000000000001</v>
       </c>
     </row>
@@ -999,7 +996,7 @@
       <c r="C3" s="6" t="n">
         <v>70.54000000000001</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="7" t="n">
         <v>57.3</v>
       </c>
       <c r="E3" s="6" t="n">
@@ -1008,34 +1005,34 @@
       <c r="F3" s="6" t="n">
         <v>0.7957</v>
       </c>
-      <c r="G3" s="8" t="n">
+      <c r="G3" s="7" t="n">
         <v>46.31</v>
       </c>
-      <c r="H3" s="8" t="n">
+      <c r="H3" s="7" t="n">
         <v>72.17</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>55.58</v>
       </c>
-      <c r="J3" s="7" t="n">
+      <c r="J3" s="5" t="n">
         <v>0.8966</v>
       </c>
-      <c r="K3" s="8" t="n">
+      <c r="K3" s="7" t="n">
         <v>0.7993</v>
       </c>
-      <c r="L3" s="7" t="n">
+      <c r="L3" s="5" t="n">
         <v>46.29</v>
       </c>
-      <c r="M3" s="7" t="n">
+      <c r="M3" s="5" t="n">
         <v>72.08</v>
       </c>
       <c r="N3" s="6" t="n">
         <v>55.58</v>
       </c>
-      <c r="O3" s="8" t="n">
+      <c r="O3" s="7" t="n">
         <v>0.8977000000000001</v>
       </c>
-      <c r="P3" s="8" t="n">
+      <c r="P3" s="7" t="n">
         <v>0.7993</v>
       </c>
     </row>
@@ -1060,34 +1057,34 @@
       <c r="F4" s="6" t="n">
         <v>0.8051</v>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="G4" s="7" t="n">
         <v>62.24</v>
       </c>
-      <c r="H4" s="8" t="n">
+      <c r="H4" s="7" t="n">
         <v>81.27</v>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="I4" s="5" t="n">
         <v>86.13</v>
       </c>
-      <c r="J4" s="7" t="n">
+      <c r="J4" s="5" t="n">
         <v>0.9074</v>
       </c>
-      <c r="K4" s="7" t="n">
+      <c r="K4" s="5" t="n">
         <v>0.8070000000000001</v>
       </c>
-      <c r="L4" s="7" t="n">
+      <c r="L4" s="5" t="n">
         <v>61.86</v>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="M4" s="5" t="n">
         <v>80.98999999999999</v>
       </c>
-      <c r="N4" s="8" t="n">
+      <c r="N4" s="7" t="n">
         <v>87.86</v>
       </c>
-      <c r="O4" s="8" t="n">
+      <c r="O4" s="7" t="n">
         <v>0.9112</v>
       </c>
-      <c r="P4" s="8" t="n">
+      <c r="P4" s="7" t="n">
         <v>0.8129</v>
       </c>
     </row>
@@ -1106,16 +1103,16 @@
       <c r="D5" s="6" t="n">
         <v>67.84</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="5" t="n">
         <v>0.8868</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>0.7043</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="7" t="n">
         <v>45.69</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H5" s="5" t="n">
         <v>71.62</v>
       </c>
       <c r="I5" s="6" t="n">
@@ -1124,22 +1121,22 @@
       <c r="J5" s="6" t="n">
         <v>0.8836000000000001</v>
       </c>
-      <c r="K5" s="7" t="n">
+      <c r="K5" s="5" t="n">
         <v>0.7082000000000001</v>
       </c>
-      <c r="L5" s="7" t="n">
+      <c r="L5" s="5" t="n">
         <v>45.45</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="7" t="n">
         <v>71.89</v>
       </c>
-      <c r="N5" s="8" t="n">
+      <c r="N5" s="7" t="n">
         <v>68.92</v>
       </c>
-      <c r="O5" s="8" t="n">
+      <c r="O5" s="7" t="n">
         <v>0.8885999999999999</v>
       </c>
-      <c r="P5" s="8" t="n">
+      <c r="P5" s="7" t="n">
         <v>0.7101</v>
       </c>
     </row>

--- a/experiments/04_lora_finetuning/report/epoch_ablation.xlsx
+++ b/experiments/04_lora_finetuning/report/epoch_ablation.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,8 +33,11 @@
     <font>
       <color rgb="00006100"/>
     </font>
+    <font>
+      <color rgb="009C6500"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +62,12 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -163,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -175,6 +184,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -693,19 +705,19 @@
       <c r="D3" s="6" t="n">
         <v>51.72</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="7" t="n">
         <v>0.8825</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="7" t="n">
         <v>0.7812</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>41.32</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="H3" s="8" t="n">
         <v>69.37</v>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="I3" s="8" t="n">
         <v>54.29</v>
       </c>
       <c r="J3" s="7" t="n">
@@ -714,19 +726,19 @@
       <c r="K3" s="7" t="n">
         <v>0.7884</v>
       </c>
-      <c r="L3" s="7" t="n">
+      <c r="L3" s="8" t="n">
         <v>41.88</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>69.23</v>
       </c>
-      <c r="N3" s="7" t="n">
+      <c r="N3" s="8" t="n">
         <v>54.29</v>
       </c>
-      <c r="O3" s="5" t="n">
+      <c r="O3" s="7" t="n">
         <v>0.89</v>
       </c>
-      <c r="P3" s="5" t="n">
+      <c r="P3" s="7" t="n">
         <v>0.7866</v>
       </c>
     </row>
@@ -745,7 +757,7 @@
       <c r="D4" s="6" t="n">
         <v>82.66</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="7" t="n">
         <v>0.9074</v>
       </c>
       <c r="F4" s="6" t="n">
@@ -757,25 +769,25 @@
       <c r="H4" s="5" t="n">
         <v>79.09</v>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="I4" s="8" t="n">
         <v>84.68000000000001</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>0.91</v>
       </c>
-      <c r="K4" s="7" t="n">
+      <c r="K4" s="8" t="n">
         <v>0.8129</v>
       </c>
-      <c r="L4" s="7" t="n">
+      <c r="L4" s="8" t="n">
         <v>58.64</v>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="M4" s="8" t="n">
         <v>79.45999999999999</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>84.39</v>
       </c>
-      <c r="O4" s="6" t="n">
+      <c r="O4" s="7" t="n">
         <v>0.9071</v>
       </c>
       <c r="P4" s="5" t="n">
@@ -797,10 +809,10 @@
       <c r="D5" s="6" t="n">
         <v>59.73</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="7" t="n">
         <v>0.8904</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <v>0.7043</v>
       </c>
       <c r="G5" s="5" t="n">
@@ -809,25 +821,25 @@
       <c r="H5" s="5" t="n">
         <v>69.33</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I5" s="8" t="n">
         <v>65.14</v>
       </c>
       <c r="J5" s="7" t="n">
         <v>0.892</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="K5" s="7" t="n">
         <v>0.7043</v>
       </c>
-      <c r="L5" s="7" t="n">
+      <c r="L5" s="8" t="n">
         <v>42.01</v>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="M5" s="8" t="n">
         <v>69.64</v>
       </c>
       <c r="N5" s="5" t="n">
         <v>63.51</v>
       </c>
-      <c r="O5" s="6" t="n">
+      <c r="O5" s="7" t="n">
         <v>0.8855</v>
       </c>
       <c r="P5" s="7" t="n">
@@ -996,25 +1008,25 @@
       <c r="C3" s="6" t="n">
         <v>70.54000000000001</v>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="8" t="n">
         <v>57.3</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="7" t="n">
         <v>0.8943</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="7" t="n">
         <v>0.7957</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="G3" s="8" t="n">
         <v>46.31</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="H3" s="8" t="n">
         <v>72.17</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>55.58</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="7" t="n">
         <v>0.8966</v>
       </c>
       <c r="K3" s="7" t="n">
@@ -1051,25 +1063,25 @@
       <c r="D4" s="6" t="n">
         <v>83.81999999999999</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="7" t="n">
         <v>0.9051</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <v>0.8051</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="G4" s="8" t="n">
         <v>62.24</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H4" s="8" t="n">
         <v>81.27</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>86.13</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="J4" s="7" t="n">
         <v>0.9074</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="K4" s="7" t="n">
         <v>0.8070000000000001</v>
       </c>
       <c r="L4" s="5" t="n">
@@ -1078,7 +1090,7 @@
       <c r="M4" s="5" t="n">
         <v>80.98999999999999</v>
       </c>
-      <c r="N4" s="7" t="n">
+      <c r="N4" s="8" t="n">
         <v>87.86</v>
       </c>
       <c r="O4" s="7" t="n">
@@ -1103,13 +1115,13 @@
       <c r="D5" s="6" t="n">
         <v>67.84</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="7" t="n">
         <v>0.8868</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <v>0.7043</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="G5" s="8" t="n">
         <v>45.69</v>
       </c>
       <c r="H5" s="5" t="n">
@@ -1118,19 +1130,19 @@
       <c r="I5" s="6" t="n">
         <v>67.84</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="7" t="n">
         <v>0.8836000000000001</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="K5" s="7" t="n">
         <v>0.7082000000000001</v>
       </c>
       <c r="L5" s="5" t="n">
         <v>45.45</v>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="M5" s="8" t="n">
         <v>71.89</v>
       </c>
-      <c r="N5" s="7" t="n">
+      <c r="N5" s="8" t="n">
         <v>68.92</v>
       </c>
       <c r="O5" s="7" t="n">
